--- a/financial_advisor_forms/001_small_business_credit_application_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/001_small_business_credit_application_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1053,8 +1053,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_1,_'label':_'6-12_months'}</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 1, 'label': '6-12 months'}</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_2,_'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 2, 'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_3,_'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 3, 'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_1,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 1, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_2,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 2, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_3,_'label':_'semi-annually'}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 3, 'label': 'Semi-annually'}</t>
+          <t>Semi-annually</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_4,_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 4, 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_1,_'label':_'limited_liability_partnership'}</t>
+          <t>limited_liability_partnership</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 1, 'label': 'Limited liability partnership'}</t>
+          <t>Limited liability partnership</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_2,_'label':_'corporation'}</t>
+          <t>corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 2, 'label': 'Corporation'}</t>
+          <t>Corporation</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_3,_'label':_'sole_proprietorship'}</t>
+          <t>sole_proprietorship</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 3, 'label': 'Sole proprietorship'}</t>
+          <t>Sole proprietorship</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_4,_'label':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 4, 'label': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 1, 'label': 'High school'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_2,_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 2, 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_3,_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 3, 'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_4,_'label':_'graduate_school'}</t>
+          <t>graduate_school</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 4, 'label': 'Graduate school'}</t>
+          <t>Graduate school</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_1,_'label':_'ein'}</t>
+          <t>ein</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 1, 'label': 'EIN'}</t>
+          <t>EIN</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_2,_'label':_'ssn'}</t>
+          <t>ssn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 2, 'label': 'SSN'}</t>
+          <t>SSN</t>
         </is>
       </c>
     </row>
